--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SEC_02_CHECK_LIST_405.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SEC_02_CHECK_LIST_405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE405_Introduction to Deep Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D6824B-184A-4ED5-BB73-A6DE9BF706F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756D128C-375D-4B63-ABA0-2A5190FC67D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="25">
   <si>
     <t>มหาวิทยาลัยเทคโนโลยีราชมงคลล้านนา เชียงราย</t>
   </si>
@@ -187,13 +187,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -510,105 +510,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -641,7 +641,9 @@
       <c r="M5" s="1">
         <v>2</v>
       </c>
-      <c r="N5" s="1"/>
+      <c r="N5" s="1">
+        <v>3</v>
+      </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -649,9 +651,9 @@
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
       <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
@@ -682,7 +684,9 @@
       <c r="M6" s="1">
         <v>20</v>
       </c>
-      <c r="N6" s="1"/>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -690,9 +694,9 @@
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.8">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
@@ -723,7 +727,9 @@
       <c r="M7" s="1">
         <v>9</v>
       </c>
-      <c r="N7" s="1"/>
+      <c r="N7" s="1">
+        <v>10</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -737,10 +743,10 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="4" t="s">
         <v>22</v>
       </c>
@@ -768,7 +774,9 @@
       <c r="M8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="3"/>
+      <c r="N8" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -782,10 +790,10 @@
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="7"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="4" t="s">
         <v>22</v>
       </c>
@@ -813,7 +821,9 @@
       <c r="M9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="3"/>
+      <c r="N9" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -827,10 +837,10 @@
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="4" t="s">
         <v>22</v>
       </c>
@@ -858,7 +868,9 @@
       <c r="M10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="3"/>
+      <c r="N10" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -872,10 +884,10 @@
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="4" t="s">
         <v>22</v>
       </c>
@@ -903,7 +915,9 @@
       <c r="M11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="3"/>
+      <c r="N11" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -917,10 +931,10 @@
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="4" t="s">
         <v>22</v>
       </c>
@@ -948,7 +962,9 @@
       <c r="M12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="3"/>
+      <c r="N12" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -962,10 +978,10 @@
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="9"/>
       <c r="E13" s="4" t="s">
         <v>23</v>
       </c>
@@ -993,7 +1009,9 @@
       <c r="M13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="3"/>
+      <c r="N13" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -1003,6 +1021,12 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="13">
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -1010,12 +1034,6 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
